--- a/E/DU3BMKT.xlsx
+++ b/E/DU3BMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="16">
   <si>
     <t/>
   </si>
   <si>
-    <t>10008989</t>
-  </si>
-  <si>
-    <t>BIMOLI MYK.GRG REF2L</t>
+    <t>10027090</t>
+  </si>
+  <si>
+    <t>SENSODYNE P/GL CG100</t>
   </si>
   <si>
     <t>DU3BMKT</t>
@@ -28,19 +28,37 @@
     <t>1</t>
   </si>
   <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>10010805</t>
-  </si>
-  <si>
-    <t>SANIA MNYK GR PCH 2L</t>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>10031825</t>
+  </si>
+  <si>
+    <t>SENSODYNE P/G FM 100</t>
+  </si>
+  <si>
+    <t>20139653</t>
+  </si>
+  <si>
+    <t>LRST FAC.TIS 2X200S</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>RT,(E-4B)</t>
+    <t>PT</t>
+  </si>
+  <si>
+    <t>20135747</t>
+  </si>
+  <si>
+    <t>MAKUKU AIR DIAP XL24</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>RT,(E-2B)</t>
   </si>
 </sst>
 </file>
@@ -433,7 +451,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -496,10 +514,50 @@
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="B4" s="1" t="s">
         <v>9</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU3BMKT.xlsx
+++ b/E/DU3BMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="23">
   <si>
     <t/>
   </si>
   <si>
-    <t>10004067</t>
-  </si>
-  <si>
-    <t>M/LMN PCH LMN 690 G</t>
+    <t>20135747</t>
+  </si>
+  <si>
+    <t>MAKUKU AIR DIAP XL24</t>
   </si>
   <si>
     <t>DU3BMKT</t>
@@ -28,67 +28,58 @@
     <t>1</t>
   </si>
   <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20141204</t>
+  </si>
+  <si>
+    <t>IDM P.PRG JR.NPS 950</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>PT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20120180</t>
+  </si>
+  <si>
+    <t>SO SOFT RS&amp;WTRLY 700</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>10004068</t>
-  </si>
-  <si>
-    <t>M/LIME POUCH 690 G</t>
-  </si>
-  <si>
-    <t>20034450</t>
-  </si>
-  <si>
-    <t>M/LMN JRK NPS 690 G</t>
-  </si>
-  <si>
-    <t>20052031</t>
-  </si>
-  <si>
-    <t>M/LIME GRN TEA 690 G</t>
-  </si>
-  <si>
-    <t>20099424</t>
-  </si>
-  <si>
-    <t>M/LIME CHARCO 690 G</t>
-  </si>
-  <si>
-    <t>20134303</t>
-  </si>
-  <si>
-    <t>M/LMN RE YUZU 690 G</t>
-  </si>
-  <si>
-    <t>RT,(E-1.5B)</t>
-  </si>
-  <si>
-    <t>20142277</t>
-  </si>
-  <si>
-    <t>M/LIME JRK BTL 690 G</t>
-  </si>
-  <si>
-    <t>20120921</t>
-  </si>
-  <si>
-    <t>GIV BW M&amp;C PH 800 ML</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>20134306</t>
-  </si>
-  <si>
-    <t>BABY HP PNTS 24S XXL</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>RT,(E-0.5B)</t>
+    <t>20121364</t>
+  </si>
+  <si>
+    <t>SO SOFT SKR BLSM 700</t>
+  </si>
+  <si>
+    <t>20128720</t>
+  </si>
+  <si>
+    <t>SO SOFT FLO BRS 700</t>
+  </si>
+  <si>
+    <t>20135246</t>
+  </si>
+  <si>
+    <t>SO SOFT SWT PEONY700</t>
+  </si>
+  <si>
+    <t>20140325</t>
+  </si>
+  <si>
+    <t>SO SOFT FLO LILY 700</t>
+  </si>
+  <si>
+    <t>RT</t>
   </si>
 </sst>
 </file>
@@ -481,13 +472,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -544,18 +535,18 @@
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -564,18 +555,18 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -584,18 +575,18 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -604,18 +595,18 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
@@ -624,18 +615,18 @@
         <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
@@ -644,50 +635,10 @@
         <v>4</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU3BMKT.xlsx
+++ b/E/DU3BMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="30">
   <si>
     <t/>
   </si>
   <si>
-    <t>20135747</t>
-  </si>
-  <si>
-    <t>MAKUKU AIR DIAP XL24</t>
+    <t>20135746</t>
+  </si>
+  <si>
+    <t>MAKUKU AIR DIAPR L26</t>
   </si>
   <si>
     <t>DU3BMKT</t>
@@ -31,55 +31,76 @@
     <t>RT,(E-2B)</t>
   </si>
   <si>
-    <t>20141204</t>
-  </si>
-  <si>
-    <t>IDM P.PRG JR.NPS 950</t>
+    <t>20113567</t>
+  </si>
+  <si>
+    <t>GNTLE GEN M.B 700 ML</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>PT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20120180</t>
-  </si>
-  <si>
-    <t>SO SOFT RS&amp;WTRLY 700</t>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20115958</t>
+  </si>
+  <si>
+    <t>GENTLE GEN PG 700 ML</t>
+  </si>
+  <si>
+    <t>20115959</t>
+  </si>
+  <si>
+    <t>GENTLE GEN FP 700 ML</t>
+  </si>
+  <si>
+    <t>20133333</t>
+  </si>
+  <si>
+    <t>GNTLE GEN A.K 700 ML</t>
+  </si>
+  <si>
+    <t>20141371</t>
+  </si>
+  <si>
+    <t>GENTLE GEN CM 700 ML</t>
+  </si>
+  <si>
+    <t>20141372</t>
+  </si>
+  <si>
+    <t>GENTLE GEN LI 700 ML</t>
+  </si>
+  <si>
+    <t>20064413</t>
+  </si>
+  <si>
+    <t>ATTACK JAZ CN 1.5 KG</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20121364</t>
-  </si>
-  <si>
-    <t>SO SOFT SKR BLSM 700</t>
-  </si>
-  <si>
-    <t>20128720</t>
-  </si>
-  <si>
-    <t>SO SOFT FLO BRS 700</t>
-  </si>
-  <si>
-    <t>20135246</t>
-  </si>
-  <si>
-    <t>SO SOFT SWT PEONY700</t>
-  </si>
-  <si>
-    <t>20140325</t>
-  </si>
-  <si>
-    <t>SO SOFT FLO LILY 700</t>
-  </si>
-  <si>
     <t>RT</t>
+  </si>
+  <si>
+    <t>20064414</t>
+  </si>
+  <si>
+    <t>ATTACK JAZ SG 1.5 KG</t>
+  </si>
+  <si>
+    <t>20130527</t>
+  </si>
+  <si>
+    <t>ATTACK JAZ RS 1.4 KG</t>
+  </si>
+  <si>
+    <t>20138108</t>
+  </si>
+  <si>
+    <t>ATTACK JAZ PR 1.4 KG</t>
   </si>
 </sst>
 </file>
@@ -472,7 +493,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -555,18 +576,18 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -575,18 +596,18 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -595,18 +616,18 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
@@ -615,30 +636,110 @@
         <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B9" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" s="1" t="s">
+      <c r="C9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>22</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
